--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -916,7 +916,11 @@
           <t>10-19 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>012682482.IB</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -1127,7 +1131,9 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-19" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-20" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-19</t>
+          <t>数据来源：DM    2026-10-20</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,11 @@
           <t>10-19 17:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>212680066.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -709,10 +713,16 @@
       <c r="E3" s="4" t="n">
         <v>15.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>30.26</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.53</t>
@@ -735,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>1.5600/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -745,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A 79.80</t>
+          <t>A 77.16</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -969,7 +979,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 39.63</t>
+          <t>B- 41.97</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -939,7 +939,9 @@
       <c r="E4" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.07</t>

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-20" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-21" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-20</t>
+          <t>数据来源：DM    2026-10-21</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A 77.16</t>
+          <t>A 78.51</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
@@ -947,8 +947,12 @@
           <t>1.80 ~ 2.07</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>91.84</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.01</t>
@@ -981,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 41.97</t>
+          <t>B- 40.87</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1004,7 +1008,9 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>0.62</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-22" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-21</t>
+          <t>数据来源：DM    2026-10-22</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A 78.51</t>
+          <t>A 77.77</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 40.87</t>
+          <t>B- 42.83</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-22" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-23" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-22</t>
+          <t>数据来源：DM    2026-10-23</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A 77.77</t>
+          <t>A 79.38</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -868,21 +868,9 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
+      <c r="AQ3" s="3"/>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3"/>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -985,7 +973,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 42.83</t>
+          <t>B- 43.37</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1104,21 +1092,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
+      <c r="AQ4" s="3"/>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3"/>
       <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>综合</t>

--- a/data/credit_bond_2026-10-19.xlsx
+++ b/data/credit_bond_2026-10-19.xlsx
@@ -868,9 +868,21 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>银行</t>
@@ -1092,9 +1104,21 @@
           <t>5</t>
         </is>
       </c>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
           <t>综合</t>
